--- a/backend/data/attachments/wealth_理财经理考核标准_8.xlsx
+++ b/backend/data/attachments/wealth_理财经理考核标准_8.xlsx
@@ -450,16 +450,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="C2" t="n">
-        <v>200</v>
+        <v>123</v>
       </c>
       <c r="D2" t="n">
-        <v>14201</v>
+        <v>6257</v>
       </c>
       <c r="E2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3">
@@ -469,13 +469,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>268</v>
+        <v>146</v>
       </c>
       <c r="C3" t="n">
-        <v>443</v>
+        <v>414</v>
       </c>
       <c r="D3" t="n">
-        <v>1500</v>
+        <v>3433</v>
       </c>
       <c r="E3" t="n">
         <v>5</v>
@@ -488,16 +488,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1224</v>
+        <v>1447</v>
       </c>
       <c r="C4" t="n">
-        <v>633</v>
+        <v>794</v>
       </c>
       <c r="D4" t="n">
-        <v>352</v>
+        <v>867</v>
       </c>
       <c r="E4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -541,14 +541,14 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>259</v>
+        <v>121</v>
       </c>
       <c r="C7" t="n">
-        <v>560</v>
+        <v>660</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>5.2%</t>
+          <t>6.8%</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -564,14 +564,14 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>94</v>
+        <v>54</v>
       </c>
       <c r="C8" t="n">
-        <v>104</v>
+        <v>132</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>9.1%</t>
+          <t>12.2%</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -587,10 +587,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="C9" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
